--- a/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Shock_Tr3Ro3.xlsx
+++ b/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Shock_Tr3Ro3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Subframe_Conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF73A09-681D-48E8-B3C3-EF3560B3916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C0B662-A6E1-40E2-BCA6-E00F98A831B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36105" yWindow="630" windowWidth="21600" windowHeight="13965" tabRatio="988" activeTab="1" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
+    <workbookView xWindow="33225" yWindow="1875" windowWidth="18825" windowHeight="11430" tabRatio="988" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
   </bookViews>
   <sheets>
     <sheet name="BushShock_Tr3Ro3_SLGf_MacP" sheetId="56" r:id="rId1"/>
@@ -2390,7 +2390,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B7:C9 B11:C29 A20 A28 B31:C33 B35:C53 A44 A52">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4113,7 +4113,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B7:C9 B11:C29 A20 A28 B31:C33 B35:C53 A44 A52">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5836,7 +5836,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B7:C9 B11:C29 A20 A28 B31:C33 B35:C53 A44 A52">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Shock_Tr3Ro3.xlsx
+++ b/Libraries/Vehicle/Linkage/Subframe_Conn/sm_car_data_Subframe_Conn_Shock_Tr3Ro3.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Linkage\Subframe_Conn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C0B662-A6E1-40E2-BCA6-E00F98A831B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C4FFDE-D1AF-4F8E-A182-3917F89DD9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33225" yWindow="1875" windowWidth="18825" windowHeight="11430" tabRatio="988" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
+    <workbookView xWindow="2340" yWindow="615" windowWidth="19275" windowHeight="12510" tabRatio="988" activeTab="2" xr2:uid="{5C9B011B-FECB-46A4-81D1-C980D278E613}"/>
   </bookViews>
   <sheets>
-    <sheet name="BushShock_Tr3Ro3_SLGf_MacP" sheetId="56" r:id="rId1"/>
-    <sheet name="BushShock_Tr3Ro3_SHf_MacP" sheetId="58" r:id="rId2"/>
-    <sheet name="BushShock_Tr3Ro3_SHr_Twi" sheetId="55" r:id="rId3"/>
+    <sheet name="SLGf_MacP_Top" sheetId="56" r:id="rId1"/>
+    <sheet name="Sef_MacP_Top" sheetId="58" r:id="rId2"/>
+    <sheet name="Ser_Twi_Top" sheetId="55" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -181,13 +181,13 @@
     <t>w</t>
   </si>
   <si>
-    <t>BushShock_Tr3Ro3_SLGf_MacP</t>
+    <t>BushShock_Tr3Ro3_Sef_MacP_Top</t>
   </si>
   <si>
-    <t>BushShock_Tr3Ro3_SHr_Twi</t>
+    <t>BushShock_Tr3Ro3_SLGf_MacP_Top</t>
   </si>
   <si>
-    <t>BushShock_Tr3Ro3_SHf_MacP</t>
+    <t>BushShock_Tr3Ro3_Ser_Twi_Top</t>
   </si>
 </sst>
 </file>
@@ -754,7 +754,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2477,7 +2477,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -4200,7 +4200,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
